--- a/Lab 02/RunningTimeRecording.xlsx
+++ b/Lab 02/RunningTimeRecording.xlsx
@@ -242,6 +242,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -251,16 +261,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,31 +554,31 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="12" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -591,7 +591,7 @@
       <c r="E4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -600,7 +600,7 @@
       <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="7" t="s">
@@ -629,7 +629,7 @@
       <c r="E5">
         <v>4.9047470000000004</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="11">
         <f>C5/E5</f>
         <v>1.328332123960726</v>
       </c>
@@ -639,7 +639,7 @@
       <c r="H5">
         <v>4.8249380000000004</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="11">
         <f>C5/H5</f>
         <v>1.3503039831807164</v>
       </c>
@@ -660,7 +660,7 @@
       <c r="E6">
         <v>5.4722660000000003</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="11">
         <f t="shared" ref="F6:F35" si="0">C6/E6</f>
         <v>1.4162208123654807</v>
       </c>
@@ -670,7 +670,7 @@
       <c r="H6">
         <v>5.4141139999999996</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="11">
         <f t="shared" ref="I6:I35" si="1">C6/H6</f>
         <v>1.4314321789308464</v>
       </c>
@@ -691,7 +691,7 @@
       <c r="E7">
         <v>6.0115309999999997</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="11">
         <f t="shared" si="0"/>
         <v>1.3445125709241126</v>
       </c>
@@ -701,7 +701,7 @@
       <c r="H7">
         <v>5.7772370000000004</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="11">
         <f t="shared" si="1"/>
         <v>1.3990388485014549</v>
       </c>
@@ -722,7 +722,7 @@
       <c r="E8">
         <v>6.5134590000000001</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="11">
         <f t="shared" si="0"/>
         <v>1.3865376292381666</v>
       </c>
@@ -732,7 +732,7 @@
       <c r="H8">
         <v>6.3767670000000001</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="11">
         <f t="shared" si="1"/>
         <v>1.4162593677956241</v>
       </c>
@@ -753,7 +753,7 @@
       <c r="E9">
         <v>7.4373189999999996</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="11">
         <f t="shared" si="0"/>
         <v>1.3245363013204086</v>
       </c>
@@ -763,7 +763,7 @@
       <c r="H9">
         <v>6.863175</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="11">
         <f t="shared" si="1"/>
         <v>1.4353413689728149</v>
       </c>
@@ -784,7 +784,7 @@
       <c r="E10">
         <v>7.6541090000000001</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="11">
         <f t="shared" si="0"/>
         <v>1.3935790566870683</v>
       </c>
@@ -794,7 +794,7 @@
       <c r="H10">
         <v>7.1307939999999999</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="11">
         <f t="shared" si="1"/>
         <v>1.4958510931601727</v>
       </c>
@@ -815,7 +815,7 @@
       <c r="E11">
         <v>8.112228</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="11">
         <f t="shared" si="0"/>
         <v>1.4305709849377999</v>
       </c>
@@ -825,7 +825,7 @@
       <c r="H11">
         <v>7.7643560000000003</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="11">
         <f t="shared" si="1"/>
         <v>1.4946658808534796</v>
       </c>
@@ -846,7 +846,7 @@
       <c r="E12">
         <v>8.8919409999999992</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="11">
         <f t="shared" si="0"/>
         <v>1.4016459398459797</v>
       </c>
@@ -856,7 +856,7 @@
       <c r="H12">
         <v>8.1383880000000008</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="11">
         <f t="shared" si="1"/>
         <v>1.5314277225416137</v>
       </c>
@@ -877,7 +877,7 @@
       <c r="E13">
         <v>9.2765090000000008</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="11">
         <f t="shared" si="0"/>
         <v>1.6029627093554264</v>
       </c>
@@ -887,7 +887,7 @@
       <c r="H13">
         <v>8.7415050000000001</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="11">
         <f t="shared" si="1"/>
         <v>1.7010684087007899</v>
       </c>
@@ -908,7 +908,7 @@
       <c r="E14">
         <v>9.7288289999999993</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="11">
         <f t="shared" si="0"/>
         <v>1.7830760515988104</v>
       </c>
@@ -918,7 +918,7 @@
       <c r="H14">
         <v>9.3940129999999993</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="11">
         <f t="shared" si="1"/>
         <v>1.8466274211032072</v>
       </c>
@@ -939,7 +939,7 @@
       <c r="E15">
         <v>10.303958</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>1.8487996554333781</v>
       </c>
@@ -949,7 +949,7 @@
       <c r="H15">
         <v>9.6902779999999993</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="11">
         <f t="shared" si="1"/>
         <v>1.9658831253344848</v>
       </c>
@@ -970,7 +970,7 @@
       <c r="E16">
         <v>11.006867</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>1.5885474949411127</v>
       </c>
@@ -980,7 +980,7 @@
       <c r="H16">
         <v>10.342828000000001</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="11">
         <f t="shared" si="1"/>
         <v>1.6905367661533188</v>
       </c>
@@ -1001,7 +1001,7 @@
       <c r="E17">
         <v>11.362147999999999</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>1.3887957629138434</v>
       </c>
@@ -1011,7 +1011,7 @@
       <c r="H17">
         <v>10.836163000000001</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="11">
         <f t="shared" si="1"/>
         <v>1.4562076078036108</v>
       </c>
@@ -1032,7 +1032,7 @@
       <c r="E18">
         <v>11.999433</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="11">
         <f t="shared" si="0"/>
         <v>1.3769903127922793</v>
       </c>
@@ -1042,7 +1042,7 @@
       <c r="H18">
         <v>11.212437</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="11">
         <f t="shared" si="1"/>
         <v>1.4736406545695642</v>
       </c>
@@ -1063,7 +1063,7 @@
       <c r="E19">
         <v>12.451181</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="11">
         <f t="shared" si="0"/>
         <v>1.4414791657112687</v>
       </c>
@@ -1073,7 +1073,7 @@
       <c r="H19">
         <v>11.945881</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="11">
         <f t="shared" si="1"/>
         <v>1.5024524352787376</v>
       </c>
@@ -1094,7 +1094,7 @@
       <c r="E20">
         <v>13.476834999999999</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="11">
         <f t="shared" si="0"/>
         <v>1.372300098650759</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="H20">
         <v>13.394746</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="11">
         <f t="shared" si="1"/>
         <v>1.3807101680016927</v>
       </c>
@@ -1125,7 +1125,7 @@
       <c r="E21">
         <v>14.402072</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>1.3252361882373591</v>
       </c>
@@ -1135,7 +1135,7 @@
       <c r="H21">
         <v>12.882567</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="11">
         <f t="shared" si="1"/>
         <v>1.4815484367362499</v>
       </c>
@@ -1156,7 +1156,7 @@
       <c r="E22">
         <v>14.169724</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="11">
         <f t="shared" si="0"/>
         <v>1.4097315515813857</v>
       </c>
@@ -1166,7 +1166,7 @@
       <c r="H22">
         <v>13.948511</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="11">
         <f t="shared" si="1"/>
         <v>1.4320888444651907</v>
       </c>
@@ -1187,7 +1187,7 @@
       <c r="E23">
         <v>15.923360000000001</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="11">
         <f t="shared" si="0"/>
         <v>1.3044582927221391</v>
       </c>
@@ -1197,7 +1197,7 @@
       <c r="H23">
         <v>13.943564</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="11">
         <f t="shared" si="1"/>
         <v>1.4896735870398701</v>
       </c>
@@ -1218,7 +1218,7 @@
       <c r="E24">
         <v>15.919912</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="11">
         <f t="shared" si="0"/>
         <v>1.368563281003061</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="H24">
         <v>14.949013000000001</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="11">
         <f t="shared" si="1"/>
         <v>1.4574478596011657</v>
       </c>
@@ -1249,7 +1249,7 @@
       <c r="E25">
         <v>17.330915999999998</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="11">
         <f t="shared" si="0"/>
         <v>1.3023222777145766</v>
       </c>
@@ -1259,7 +1259,7 @@
       <c r="H25">
         <v>15.336928</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="11">
         <f t="shared" si="1"/>
         <v>1.471640083333507</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="E26">
         <v>17.443066999999999</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="11">
         <f t="shared" si="0"/>
         <v>1.3483194784495183</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="H26">
         <v>16.241945999999999</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="11">
         <f t="shared" si="1"/>
         <v>1.4480301190510056</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="E27">
         <v>17.841816000000001</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="11">
         <f t="shared" si="0"/>
         <v>1.3670769836433689</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="H27">
         <v>16.480862999999999</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="11">
         <f t="shared" si="1"/>
         <v>1.4799671594867332</v>
       </c>
@@ -1342,7 +1342,7 @@
       <c r="E28">
         <v>18.121545000000001</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="11">
         <f t="shared" si="0"/>
         <v>1.401437018753092</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="H28">
         <v>17.078358000000001</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="11">
         <f t="shared" si="1"/>
         <v>1.4870401475364317</v>
       </c>
@@ -1373,7 +1373,7 @@
       <c r="E29">
         <v>18.265045000000001</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="11">
         <f t="shared" si="0"/>
         <v>1.433092445159593</v>
       </c>
@@ -1383,7 +1383,7 @@
       <c r="H29">
         <v>18.023268000000002</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="11">
         <f t="shared" si="1"/>
         <v>1.4523169715947184</v>
       </c>
@@ -1404,7 +1404,7 @@
       <c r="E30">
         <v>20.734860000000001</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="11">
         <f t="shared" si="0"/>
         <v>1.302595146531011</v>
       </c>
@@ -1414,7 +1414,7 @@
       <c r="H30">
         <v>18.830981000000001</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="11">
         <f t="shared" si="1"/>
         <v>1.4342921380463396</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="E31">
         <v>20.166205000000001</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="11">
         <f t="shared" si="0"/>
         <v>1.558142595495781</v>
       </c>
@@ -1445,7 +1445,7 @@
       <c r="H31">
         <v>18.517716</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="11">
         <f t="shared" si="1"/>
         <v>1.6968519767772656</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="E32">
         <v>21.138085</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="11">
         <f t="shared" si="0"/>
         <v>1.3812155642292101</v>
       </c>
@@ -1476,7 +1476,7 @@
       <c r="H32">
         <v>19.112082000000001</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="11">
         <f t="shared" si="1"/>
         <v>1.5276332531432211</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="E33">
         <v>21.486606999999999</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="11">
         <f t="shared" si="0"/>
         <v>1.6116111305987029</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="H33">
         <v>20.485202000000001</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="11">
         <f t="shared" si="1"/>
         <v>1.6903936314613837</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="E34">
         <v>22.267797000000002</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="11">
         <f t="shared" si="0"/>
         <v>1.3752990922272192</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="H34">
         <v>21.664701999999998</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="11">
         <f t="shared" si="1"/>
         <v>1.4135842256219358</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="E35">
         <v>23.259148</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="11">
         <f t="shared" si="0"/>
         <v>1.3607128257664469</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="H35">
         <v>21.150344</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="11">
         <f t="shared" si="1"/>
         <v>1.4963832739552605</v>
       </c>
@@ -1581,31 +1581,31 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="15"/>
+      <c r="D38" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="10" t="s">
+      <c r="E38" s="16"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="12" t="s">
+      <c r="H38" s="16"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="14"/>
+      <c r="A39" s="13"/>
       <c r="B39" s="6" t="s">
         <v>7</v>
       </c>
@@ -1987,16 +1987,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="J38:L38"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lab 02/RunningTimeRecording.xlsx
+++ b/Lab 02/RunningTimeRecording.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\Lab 02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9098E8CD-254D-4E6F-95BB-70EDF21D51D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4188751A-36B8-4E35-A19B-ED5FE3ABCEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runtime" sheetId="1" r:id="rId1"/>
@@ -246,12 +246,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -260,6 +254,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,43 +542,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L75"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="12" width="12.6328125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="14" t="s">
+      <c r="E3" s="14"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="16" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16"/>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>10000000</v>
       </c>
@@ -644,7 +644,7 @@
         <v>1.3503039831807164</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>11000000</v>
       </c>
@@ -675,7 +675,7 @@
         <v>1.4314321789308464</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>12000000</v>
       </c>
@@ -706,7 +706,7 @@
         <v>1.3990388485014549</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>13000000</v>
       </c>
@@ -737,7 +737,7 @@
         <v>1.4162593677956241</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>14000000</v>
       </c>
@@ -768,7 +768,7 @@
         <v>1.4353413689728149</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>15000000</v>
       </c>
@@ -799,7 +799,7 @@
         <v>1.4958510931601727</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>16000000</v>
       </c>
@@ -830,7 +830,7 @@
         <v>1.4946658808534796</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>17000000</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1.5314277225416137</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>18000000</v>
       </c>
@@ -892,7 +892,7 @@
         <v>1.7010684087007899</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>19000000</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1.8466274211032072</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>20000000</v>
       </c>
@@ -954,7 +954,7 @@
         <v>1.9658831253344848</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>21000000</v>
       </c>
@@ -985,7 +985,7 @@
         <v>1.6905367661533188</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>22000000</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>1.4562076078036108</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>23000000</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>1.4736406545695642</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>24000000</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>1.5024524352787376</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>25000000</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>1.3807101680016927</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>26000000</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>1.4815484367362499</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>27000000</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>1.4320888444651907</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>28000000</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>1.4896735870398701</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>29000000</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>1.4574478596011657</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>30000000</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>1.471640083333507</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>31000000</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>1.4480301190510056</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>32000000</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>1.4799671594867332</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>33000000</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>1.4870401475364317</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>34000000</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>1.4523169715947184</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>35000000</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>1.4342921380463396</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>36000000</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>1.6968519767772656</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>37000000</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>1.5276332531432211</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>38000000</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>1.6903936314613837</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>39000000</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>1.4135842256219358</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>40000000</v>
       </c>
@@ -1574,38 +1574,38 @@
         <v>1.4963832739552605</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="14" t="s">
+      <c r="C38" s="13"/>
+      <c r="D38" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="14" t="s">
+      <c r="E38" s="14"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="16"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="16" t="s">
+      <c r="H38" s="14"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="13"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="16"/>
       <c r="B39" s="6" t="s">
         <v>7</v>
       </c>
@@ -1640,363 +1640,488 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>10000000</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="5"/>
+      <c r="B40">
+        <v>1.4670300000000001</v>
+      </c>
+      <c r="C40">
+        <v>7.1804699999999997</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="F40" s="5"/>
       <c r="G40" s="4"/>
       <c r="I40" s="5"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>11000000</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="5"/>
+      <c r="B41">
+        <v>2.0226090000000001</v>
+      </c>
+      <c r="C41">
+        <v>7.876093</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="I41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>12000000</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="5"/>
+      <c r="B42">
+        <v>2.3175219999999999</v>
+      </c>
+      <c r="C42">
+        <v>8.9325740000000007</v>
+      </c>
       <c r="D42" s="4"/>
       <c r="F42" s="5"/>
       <c r="G42" s="4"/>
       <c r="I42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>13000000</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
+      <c r="B43">
+        <v>2.6005850000000001</v>
+      </c>
+      <c r="C43">
+        <v>9.2416009999999993</v>
+      </c>
       <c r="D43" s="4"/>
       <c r="F43" s="5"/>
       <c r="G43" s="4"/>
       <c r="I43" s="5"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>14000000</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="5"/>
+      <c r="B44">
+        <v>2.8971390000000001</v>
+      </c>
+      <c r="C44">
+        <v>10.735709</v>
+      </c>
       <c r="D44" s="4"/>
       <c r="F44" s="5"/>
       <c r="G44" s="4"/>
       <c r="I44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>15000000</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
+      <c r="B45">
+        <v>3.163754</v>
+      </c>
+      <c r="C45">
+        <v>11.866488</v>
+      </c>
       <c r="D45" s="4"/>
       <c r="F45" s="5"/>
       <c r="G45" s="4"/>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>16000000</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
+      <c r="B46">
+        <v>3.4311189999999998</v>
+      </c>
+      <c r="C46">
+        <v>12.572615000000001</v>
+      </c>
       <c r="D46" s="4"/>
       <c r="F46" s="5"/>
       <c r="G46" s="4"/>
       <c r="I46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>17000000</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
+      <c r="B47">
+        <v>3.7426620000000002</v>
+      </c>
+      <c r="C47">
+        <v>12.546885</v>
+      </c>
       <c r="D47" s="4"/>
       <c r="F47" s="5"/>
       <c r="G47" s="4"/>
       <c r="I47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>18000000</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
+      <c r="B48">
+        <v>4.2139559999999996</v>
+      </c>
+      <c r="C48">
+        <v>14.723947000000001</v>
+      </c>
       <c r="D48" s="4"/>
       <c r="F48" s="5"/>
       <c r="G48" s="4"/>
       <c r="I48" s="5"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>19000000</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="5"/>
+      <c r="B49">
+        <v>4.5418440000000002</v>
+      </c>
+      <c r="C49">
+        <v>14.086270000000001</v>
+      </c>
       <c r="D49" s="4"/>
       <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="I49" s="5"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>20000000</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="5"/>
+      <c r="B50">
+        <v>4.7881710000000002</v>
+      </c>
+      <c r="C50">
+        <v>14.306535</v>
+      </c>
       <c r="D50" s="4"/>
       <c r="F50" s="5"/>
       <c r="G50" s="4"/>
       <c r="I50" s="5"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>21000000</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="5"/>
+      <c r="B51">
+        <v>5.1194030000000001</v>
+      </c>
+      <c r="C51">
+        <v>16.77722</v>
+      </c>
       <c r="D51" s="4"/>
       <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="I51" s="5"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>22000000</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
+      <c r="B52">
+        <v>5.5305020000000003</v>
+      </c>
+      <c r="C52">
+        <v>18.731389</v>
+      </c>
       <c r="D52" s="4"/>
       <c r="F52" s="5"/>
       <c r="G52" s="4"/>
       <c r="I52" s="5"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>23000000</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
+      <c r="B53">
+        <v>5.9119820000000001</v>
+      </c>
+      <c r="C53">
+        <v>19.619128</v>
+      </c>
       <c r="D53" s="4"/>
       <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>24000000</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
+      <c r="B54">
+        <v>6.2716409999999998</v>
+      </c>
+      <c r="C54">
+        <v>19.129785999999999</v>
+      </c>
       <c r="D54" s="4"/>
       <c r="F54" s="5"/>
       <c r="G54" s="4"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>25000000</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="5"/>
+      <c r="B55">
+        <v>6.5090339999999998</v>
+      </c>
+      <c r="C55">
+        <v>19.475451</v>
+      </c>
       <c r="D55" s="4"/>
       <c r="F55" s="5"/>
       <c r="G55" s="4"/>
       <c r="I55" s="5"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>26000000</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
+      <c r="B56">
+        <v>6.8923880000000004</v>
+      </c>
+      <c r="C56">
+        <v>20.863251999999999</v>
+      </c>
       <c r="D56" s="4"/>
       <c r="F56" s="5"/>
       <c r="G56" s="4"/>
       <c r="I56" s="5"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>27000000</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="5"/>
+      <c r="B57">
+        <v>7.5221939999999998</v>
+      </c>
+      <c r="C57">
+        <v>31.162883999999998</v>
+      </c>
       <c r="D57" s="4"/>
       <c r="F57" s="5"/>
       <c r="G57" s="4"/>
       <c r="I57" s="5"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>28000000</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
+      <c r="B58">
+        <v>7.5826880000000001</v>
+      </c>
+      <c r="C58">
+        <v>24.242832</v>
+      </c>
       <c r="D58" s="4"/>
       <c r="F58" s="5"/>
       <c r="G58" s="4"/>
       <c r="I58" s="5"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>29000000</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
+      <c r="B59">
+        <v>7.928973</v>
+      </c>
+      <c r="C59">
+        <v>23.477260000000001</v>
+      </c>
       <c r="D59" s="4"/>
       <c r="F59" s="5"/>
       <c r="G59" s="4"/>
       <c r="I59" s="5"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>30000000</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="5"/>
+      <c r="B60">
+        <v>8.360716</v>
+      </c>
+      <c r="C60">
+        <v>26.170957999999999</v>
+      </c>
       <c r="D60" s="4"/>
       <c r="F60" s="5"/>
       <c r="G60" s="4"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>31000000</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="5"/>
+      <c r="B61">
+        <v>8.7009120000000006</v>
+      </c>
+      <c r="C61">
+        <v>24.775784999999999</v>
+      </c>
       <c r="D61" s="4"/>
       <c r="F61" s="5"/>
       <c r="G61" s="4"/>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>32000000</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="5"/>
+      <c r="B62">
+        <v>9.1592319999999994</v>
+      </c>
+      <c r="C62">
+        <v>26.441016000000001</v>
+      </c>
       <c r="D62" s="4"/>
       <c r="F62" s="5"/>
       <c r="G62" s="4"/>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>33000000</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="5"/>
+      <c r="B63">
+        <v>9.6805749999999993</v>
+      </c>
+      <c r="C63">
+        <v>28.407530000000001</v>
+      </c>
       <c r="D63" s="4"/>
       <c r="F63" s="5"/>
       <c r="G63" s="4"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>34000000</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="5"/>
+      <c r="B64">
+        <v>9.9461390000000005</v>
+      </c>
+      <c r="C64">
+        <v>26.448874</v>
+      </c>
       <c r="D64" s="4"/>
       <c r="F64" s="5"/>
       <c r="G64" s="4"/>
       <c r="I64" s="5"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>35000000</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="5"/>
+      <c r="B65">
+        <v>10.683282999999999</v>
+      </c>
+      <c r="C65">
+        <v>29.509153999999999</v>
+      </c>
       <c r="D65" s="4"/>
       <c r="F65" s="5"/>
       <c r="G65" s="4"/>
       <c r="I65" s="5"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>36000000</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="5"/>
+      <c r="B66">
+        <v>10.981681</v>
+      </c>
+      <c r="C66">
+        <v>28.635020000000001</v>
+      </c>
       <c r="D66" s="4"/>
       <c r="F66" s="5"/>
       <c r="G66" s="4"/>
       <c r="I66" s="5"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>37000000</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="5"/>
+      <c r="B67">
+        <v>11.572463000000001</v>
+      </c>
+      <c r="C67">
+        <v>32.200043999999998</v>
+      </c>
       <c r="D67" s="4"/>
       <c r="F67" s="5"/>
       <c r="G67" s="4"/>
       <c r="I67" s="5"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>38000000</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="5"/>
+      <c r="B68">
+        <v>11.990257</v>
+      </c>
+      <c r="C68">
+        <v>33.297845000000002</v>
+      </c>
       <c r="D68" s="4"/>
       <c r="F68" s="5"/>
       <c r="G68" s="4"/>
       <c r="I68" s="5"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>39000000</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="5"/>
+      <c r="B69">
+        <v>12.124834999999999</v>
+      </c>
+      <c r="C69">
+        <v>32.234180000000002</v>
+      </c>
       <c r="D69" s="4"/>
       <c r="F69" s="5"/>
       <c r="G69" s="4"/>
       <c r="I69" s="5"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>40000000</v>
       </c>
-      <c r="C70" s="5"/>
+      <c r="B70">
+        <v>12.632493</v>
+      </c>
+      <c r="C70">
+        <v>39.300693000000003</v>
+      </c>
       <c r="D70" s="4"/>
       <c r="F70" s="5"/>
       <c r="G70" s="4"/>
       <c r="I70" s="5"/>
     </row>
-    <row r="75" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="J38:L38"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="J38:L38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lab 02/RunningTimeRecording.xlsx
+++ b/Lab 02/RunningTimeRecording.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\Lab 02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4188751A-36B8-4E35-A19B-ED5FE3ABCEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F4A27-63DE-4E60-95B6-FD63419CBE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -246,6 +245,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -579,37 +579,37 @@
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="B5">
         <v>2.029636</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>6.5151329999999996</v>
       </c>
       <c r="D5">
@@ -629,7 +629,7 @@
       <c r="E5">
         <v>4.9047470000000004</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>C5/E5</f>
         <v>1.328332123960726</v>
       </c>
@@ -639,7 +639,7 @@
       <c r="H5">
         <v>4.8249380000000004</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <f>C5/H5</f>
         <v>1.3503039831807164</v>
       </c>
@@ -651,7 +651,7 @@
       <c r="B6">
         <v>2.3528410000000002</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>7.7499370000000001</v>
       </c>
       <c r="D6">
@@ -660,7 +660,7 @@
       <c r="E6">
         <v>5.4722660000000003</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f t="shared" ref="F6:F35" si="0">C6/E6</f>
         <v>1.4162208123654807</v>
       </c>
@@ -670,7 +670,7 @@
       <c r="H6">
         <v>5.4141139999999996</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <f t="shared" ref="I6:I35" si="1">C6/H6</f>
         <v>1.4314321789308464</v>
       </c>
@@ -682,7 +682,7 @@
       <c r="B7">
         <v>2.6585930000000002</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>8.0825790000000008</v>
       </c>
       <c r="D7">
@@ -691,7 +691,7 @@
       <c r="E7">
         <v>6.0115309999999997</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>1.3445125709241126</v>
       </c>
@@ -701,7 +701,7 @@
       <c r="H7">
         <v>5.7772370000000004</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <f t="shared" si="1"/>
         <v>1.3990388485014549</v>
       </c>
@@ -713,7 +713,7 @@
       <c r="B8">
         <v>2.9912550000000002</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>9.0311559999999993</v>
       </c>
       <c r="D8">
@@ -722,7 +722,7 @@
       <c r="E8">
         <v>6.5134590000000001</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>1.3865376292381666</v>
       </c>
@@ -732,7 +732,7 @@
       <c r="H8">
         <v>6.3767670000000001</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <f t="shared" si="1"/>
         <v>1.4162593677956241</v>
       </c>
@@ -744,7 +744,7 @@
       <c r="B9">
         <v>3.3147579999999999</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>9.8509989999999998</v>
       </c>
       <c r="D9">
@@ -753,7 +753,7 @@
       <c r="E9">
         <v>7.4373189999999996</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>1.3245363013204086</v>
       </c>
@@ -763,7 +763,7 @@
       <c r="H9">
         <v>6.863175</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <f t="shared" si="1"/>
         <v>1.4353413689728149</v>
       </c>
@@ -775,7 +775,7 @@
       <c r="B10">
         <v>3.6340150000000002</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>10.666606</v>
       </c>
       <c r="D10">
@@ -784,7 +784,7 @@
       <c r="E10">
         <v>7.6541090000000001</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
         <v>1.3935790566870683</v>
       </c>
@@ -794,7 +794,7 @@
       <c r="H10">
         <v>7.1307939999999999</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <f t="shared" si="1"/>
         <v>1.4958510931601727</v>
       </c>
@@ -806,7 +806,7 @@
       <c r="B11">
         <v>3.9892430000000001</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>11.605117999999999</v>
       </c>
       <c r="D11">
@@ -815,7 +815,7 @@
       <c r="E11">
         <v>8.112228</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
         <v>1.4305709849377999</v>
       </c>
@@ -825,7 +825,7 @@
       <c r="H11">
         <v>7.7643560000000003</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <f t="shared" si="1"/>
         <v>1.4946658808534796</v>
       </c>
@@ -837,7 +837,7 @@
       <c r="B12">
         <v>4.371194</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>12.463353</v>
       </c>
       <c r="D12">
@@ -846,7 +846,7 @@
       <c r="E12">
         <v>8.8919409999999992</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>1.4016459398459797</v>
       </c>
@@ -856,7 +856,7 @@
       <c r="H12">
         <v>8.1383880000000008</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <f t="shared" si="1"/>
         <v>1.5314277225416137</v>
       </c>
@@ -868,7 +868,7 @@
       <c r="B13">
         <v>4.7533820000000002</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>14.869897999999999</v>
       </c>
       <c r="D13">
@@ -877,7 +877,7 @@
       <c r="E13">
         <v>9.2765090000000008</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>1.6029627093554264</v>
       </c>
@@ -887,7 +887,7 @@
       <c r="H13">
         <v>8.7415050000000001</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <f t="shared" si="1"/>
         <v>1.7010684087007899</v>
       </c>
@@ -899,7 +899,7 @@
       <c r="B14">
         <v>5.1639609999999996</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>17.347242000000001</v>
       </c>
       <c r="D14">
@@ -908,7 +908,7 @@
       <c r="E14">
         <v>9.7288289999999993</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f t="shared" si="0"/>
         <v>1.7830760515988104</v>
       </c>
@@ -918,7 +918,7 @@
       <c r="H14">
         <v>9.3940129999999993</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="10">
         <f t="shared" si="1"/>
         <v>1.8466274211032072</v>
       </c>
@@ -930,7 +930,7 @@
       <c r="B15">
         <v>6.026249</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>19.049954</v>
       </c>
       <c r="D15">
@@ -939,7 +939,7 @@
       <c r="E15">
         <v>10.303958</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
         <v>1.8487996554333781</v>
       </c>
@@ -949,7 +949,7 @@
       <c r="H15">
         <v>9.6902779999999993</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <f t="shared" si="1"/>
         <v>1.9658831253344848</v>
       </c>
@@ -961,7 +961,7 @@
       <c r="B16">
         <v>6.8896620000000004</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>17.484931</v>
       </c>
       <c r="D16">
@@ -970,7 +970,7 @@
       <c r="E16">
         <v>11.006867</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>1.5885474949411127</v>
       </c>
@@ -980,7 +980,7 @@
       <c r="H16">
         <v>10.342828000000001</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="10">
         <f t="shared" si="1"/>
         <v>1.6905367661533188</v>
       </c>
@@ -992,7 +992,7 @@
       <c r="B17">
         <v>6.324884</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>15.779703</v>
       </c>
       <c r="D17">
@@ -1001,7 +1001,7 @@
       <c r="E17">
         <v>11.362147999999999</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f t="shared" si="0"/>
         <v>1.3887957629138434</v>
       </c>
@@ -1011,7 +1011,7 @@
       <c r="H17">
         <v>10.836163000000001</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <f t="shared" si="1"/>
         <v>1.4562076078036108</v>
       </c>
@@ -1023,7 +1023,7 @@
       <c r="B18">
         <v>6.6146240000000001</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>16.523102999999999</v>
       </c>
       <c r="D18">
@@ -1032,7 +1032,7 @@
       <c r="E18">
         <v>11.999433</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f t="shared" si="0"/>
         <v>1.3769903127922793</v>
       </c>
@@ -1042,7 +1042,7 @@
       <c r="H18">
         <v>11.212437</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="10">
         <f t="shared" si="1"/>
         <v>1.4736406545695642</v>
       </c>
@@ -1054,7 +1054,7 @@
       <c r="B19">
         <v>7.2491479999999999</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>17.948118000000001</v>
       </c>
       <c r="D19">
@@ -1063,7 +1063,7 @@
       <c r="E19">
         <v>12.451181</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <f t="shared" si="0"/>
         <v>1.4414791657112687</v>
       </c>
@@ -1073,7 +1073,7 @@
       <c r="H19">
         <v>11.945881</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="10">
         <f t="shared" si="1"/>
         <v>1.5024524352787376</v>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="B20">
         <v>7.6734749999999998</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>18.494261999999999</v>
       </c>
       <c r="D20">
@@ -1094,7 +1094,7 @@
       <c r="E20">
         <v>13.476834999999999</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <f t="shared" si="0"/>
         <v>1.372300098650759</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="H20">
         <v>13.394746</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <f t="shared" si="1"/>
         <v>1.3807101680016927</v>
       </c>
@@ -1116,7 +1116,7 @@
       <c r="B21">
         <v>7.8652139999999999</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>19.086147</v>
       </c>
       <c r="D21">
@@ -1125,7 +1125,7 @@
       <c r="E21">
         <v>14.402072</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <f t="shared" si="0"/>
         <v>1.3252361882373591</v>
       </c>
@@ -1135,7 +1135,7 @@
       <c r="H21">
         <v>12.882567</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <f t="shared" si="1"/>
         <v>1.4815484367362499</v>
       </c>
@@ -1147,7 +1147,7 @@
       <c r="B22">
         <v>8.2516970000000001</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>19.975507</v>
       </c>
       <c r="D22">
@@ -1156,7 +1156,7 @@
       <c r="E22">
         <v>14.169724</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <f t="shared" si="0"/>
         <v>1.4097315515813857</v>
       </c>
@@ -1166,7 +1166,7 @@
       <c r="H22">
         <v>13.948511</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="10">
         <f t="shared" si="1"/>
         <v>1.4320888444651907</v>
       </c>
@@ -1178,7 +1178,7 @@
       <c r="B23">
         <v>8.7318049999999996</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>20.771359</v>
       </c>
       <c r="D23">
@@ -1187,7 +1187,7 @@
       <c r="E23">
         <v>15.923360000000001</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="10">
         <f t="shared" si="0"/>
         <v>1.3044582927221391</v>
       </c>
@@ -1197,7 +1197,7 @@
       <c r="H23">
         <v>13.943564</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="10">
         <f t="shared" si="1"/>
         <v>1.4896735870398701</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="B24">
         <v>9.2346570000000003</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>21.787407000000002</v>
       </c>
       <c r="D24">
@@ -1218,7 +1218,7 @@
       <c r="E24">
         <v>15.919912</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <f t="shared" si="0"/>
         <v>1.368563281003061</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="H24">
         <v>14.949013000000001</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="10">
         <f t="shared" si="1"/>
         <v>1.4574478596011657</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="B25">
         <v>9.6331050000000005</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>22.570437999999999</v>
       </c>
       <c r="D25">
@@ -1249,7 +1249,7 @@
       <c r="E25">
         <v>17.330915999999998</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="10">
         <f t="shared" si="0"/>
         <v>1.3023222777145766</v>
       </c>
@@ -1259,7 +1259,7 @@
       <c r="H25">
         <v>15.336928</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="10">
         <f t="shared" si="1"/>
         <v>1.471640083333507</v>
       </c>
@@ -1271,7 +1271,7 @@
       <c r="B26">
         <v>10.169124</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>23.518827000000002</v>
       </c>
       <c r="D26">
@@ -1280,7 +1280,7 @@
       <c r="E26">
         <v>17.443066999999999</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <f t="shared" si="0"/>
         <v>1.3483194784495183</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="H26">
         <v>16.241945999999999</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="10">
         <f t="shared" si="1"/>
         <v>1.4480301190510056</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="B27">
         <v>10.612712999999999</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>24.391135999999999</v>
       </c>
       <c r="D27">
@@ -1311,7 +1311,7 @@
       <c r="E27">
         <v>17.841816000000001</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="10">
         <f t="shared" si="0"/>
         <v>1.3670769836433689</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="H27">
         <v>16.480862999999999</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <f t="shared" si="1"/>
         <v>1.4799671594867332</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="B28">
         <v>11.162171000000001</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>25.396204000000001</v>
       </c>
       <c r="D28">
@@ -1342,7 +1342,7 @@
       <c r="E28">
         <v>18.121545000000001</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <f t="shared" si="0"/>
         <v>1.401437018753092</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="H28">
         <v>17.078358000000001</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="10">
         <f t="shared" si="1"/>
         <v>1.4870401475364317</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="B29">
         <v>11.48982</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>26.175498000000001</v>
       </c>
       <c r="D29">
@@ -1373,7 +1373,7 @@
       <c r="E29">
         <v>18.265045000000001</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="10">
         <f t="shared" si="0"/>
         <v>1.433092445159593</v>
       </c>
@@ -1383,7 +1383,7 @@
       <c r="H29">
         <v>18.023268000000002</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="10">
         <f t="shared" si="1"/>
         <v>1.4523169715947184</v>
       </c>
@@ -1395,7 +1395,7 @@
       <c r="B30">
         <v>11.917968999999999</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>27.009128</v>
       </c>
       <c r="D30">
@@ -1404,7 +1404,7 @@
       <c r="E30">
         <v>20.734860000000001</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <f t="shared" si="0"/>
         <v>1.302595146531011</v>
       </c>
@@ -1414,7 +1414,7 @@
       <c r="H30">
         <v>18.830981000000001</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="10">
         <f t="shared" si="1"/>
         <v>1.4342921380463396</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="B31">
         <v>12.552960000000001</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4">
         <v>31.421823</v>
       </c>
       <c r="D31">
@@ -1435,7 +1435,7 @@
       <c r="E31">
         <v>20.166205000000001</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="10">
         <f t="shared" si="0"/>
         <v>1.558142595495781</v>
       </c>
@@ -1445,7 +1445,7 @@
       <c r="H31">
         <v>18.517716</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="10">
         <f t="shared" si="1"/>
         <v>1.6968519767772656</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="B32">
         <v>13.093522999999999</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="4">
         <v>29.196252000000001</v>
       </c>
       <c r="D32">
@@ -1466,7 +1466,7 @@
       <c r="E32">
         <v>21.138085</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="10">
         <f t="shared" si="0"/>
         <v>1.3812155642292101</v>
       </c>
@@ -1476,7 +1476,7 @@
       <c r="H32">
         <v>19.112082000000001</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="10">
         <f t="shared" si="1"/>
         <v>1.5276332531432211</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="B33">
         <v>13.550990000000001</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="4">
         <v>34.628055000000003</v>
       </c>
       <c r="D33">
@@ -1497,7 +1497,7 @@
       <c r="E33">
         <v>21.486606999999999</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="10">
         <f t="shared" si="0"/>
         <v>1.6116111305987029</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="H33">
         <v>20.485202000000001</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="10">
         <f t="shared" si="1"/>
         <v>1.6903936314613837</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="B34">
         <v>13.942291000000001</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>30.624880999999998</v>
       </c>
       <c r="D34">
@@ -1528,7 +1528,7 @@
       <c r="E34">
         <v>22.267797000000002</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <f t="shared" si="0"/>
         <v>1.3752990922272192</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="H34">
         <v>21.664701999999998</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="10">
         <f t="shared" si="1"/>
         <v>1.4135842256219358</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="B35">
         <v>14.453973</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4">
         <v>31.649021000000001</v>
       </c>
       <c r="D35">
@@ -1559,7 +1559,7 @@
       <c r="E35">
         <v>23.259148</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="10">
         <f t="shared" si="0"/>
         <v>1.3607128257664469</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="H35">
         <v>21.150344</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="10">
         <f t="shared" si="1"/>
         <v>1.4963832739552605</v>
       </c>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16"/>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1615,28 +1615,28 @@
       <c r="D39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1647,13 +1647,29 @@
       <c r="B40">
         <v>1.4670300000000001</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="8">
         <v>7.1804699999999997</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="4"/>
-      <c r="I40" s="5"/>
+      <c r="D40">
+        <v>0.18890199999999999</v>
+      </c>
+      <c r="E40">
+        <v>6.0646570000000004</v>
+      </c>
+      <c r="F40" s="10">
+        <f>C40/E40</f>
+        <v>1.1839861677255612</v>
+      </c>
+      <c r="G40">
+        <v>0.18970400000000001</v>
+      </c>
+      <c r="H40">
+        <v>5.7884679999999999</v>
+      </c>
+      <c r="I40" s="10">
+        <f>C40/H40</f>
+        <v>1.2404784823894681</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
@@ -1662,13 +1678,29 @@
       <c r="B41">
         <v>2.0226090000000001</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="4">
         <v>7.876093</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="4"/>
-      <c r="I41" s="5"/>
+      <c r="D41">
+        <v>0.32543699999999998</v>
+      </c>
+      <c r="E41">
+        <v>6.3765419999999997</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" ref="F41:F70" si="2">C41/E41</f>
+        <v>1.2351668035747276</v>
+      </c>
+      <c r="G41">
+        <v>0.24193100000000001</v>
+      </c>
+      <c r="H41">
+        <v>6.1801500000000003</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" ref="I41:I70" si="3">C41/H41</f>
+        <v>1.2744177730313988</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
@@ -1677,13 +1709,29 @@
       <c r="B42">
         <v>2.3175219999999999</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="4">
         <v>8.9325740000000007</v>
       </c>
-      <c r="D42" s="4"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="4"/>
-      <c r="I42" s="5"/>
+      <c r="D42">
+        <v>0.32516499999999998</v>
+      </c>
+      <c r="E42">
+        <v>7.9165239999999999</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="2"/>
+        <v>1.1283454708152216</v>
+      </c>
+      <c r="G42">
+        <v>0.26310699999999998</v>
+      </c>
+      <c r="H42">
+        <v>5.6647420000000004</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5768721682293738</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
@@ -1692,13 +1740,29 @@
       <c r="B43">
         <v>2.6005850000000001</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="4">
         <v>9.2416009999999993</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="D43">
+        <v>0.41625299999999998</v>
+      </c>
+      <c r="E43">
+        <v>8.3043359999999993</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="2"/>
+        <v>1.1128645324562976</v>
+      </c>
+      <c r="G43">
+        <v>0.339698</v>
+      </c>
+      <c r="H43">
+        <v>6.5880400000000003</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4027845914718184</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
@@ -1707,13 +1771,29 @@
       <c r="B44">
         <v>2.8971390000000001</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="4">
         <v>10.735709</v>
       </c>
-      <c r="D44" s="4"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="4"/>
-      <c r="I44" s="5"/>
+      <c r="D44">
+        <v>0.356854</v>
+      </c>
+      <c r="E44">
+        <v>7.6554010000000003</v>
+      </c>
+      <c r="F44" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4023705616466073</v>
+      </c>
+      <c r="G44">
+        <v>0.41145500000000002</v>
+      </c>
+      <c r="H44">
+        <v>7.4107130000000003</v>
+      </c>
+      <c r="I44" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4486742368784218</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
@@ -1722,13 +1802,29 @@
       <c r="B45">
         <v>3.163754</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="4">
         <v>11.866488</v>
       </c>
-      <c r="D45" s="4"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="4"/>
-      <c r="I45" s="5"/>
+      <c r="D45">
+        <v>0.43931500000000001</v>
+      </c>
+      <c r="E45">
+        <v>8.3595839999999999</v>
+      </c>
+      <c r="F45" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4195069993913574</v>
+      </c>
+      <c r="G45">
+        <v>0.436998</v>
+      </c>
+      <c r="H45">
+        <v>8.9019220000000008</v>
+      </c>
+      <c r="I45" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3330253848550908</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
@@ -1737,13 +1833,29 @@
       <c r="B46">
         <v>3.4311189999999998</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="4">
         <v>12.572615000000001</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="4"/>
-      <c r="I46" s="5"/>
+      <c r="D46">
+        <v>0.473165</v>
+      </c>
+      <c r="E46">
+        <v>8.460934</v>
+      </c>
+      <c r="F46" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4859606516254589</v>
+      </c>
+      <c r="G46">
+        <v>0.44508399999999998</v>
+      </c>
+      <c r="H46">
+        <v>8.1770040000000002</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5375576433617986</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
@@ -1752,13 +1864,29 @@
       <c r="B47">
         <v>3.7426620000000002</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="4">
         <v>12.546885</v>
       </c>
-      <c r="D47" s="4"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="4"/>
-      <c r="I47" s="5"/>
+      <c r="D47">
+        <v>0.49949300000000002</v>
+      </c>
+      <c r="E47">
+        <v>8.9979010000000006</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="2"/>
+        <v>1.3944235438909585</v>
+      </c>
+      <c r="G47">
+        <v>0.420682</v>
+      </c>
+      <c r="H47">
+        <v>8.8435889999999997</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4187548742936833</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
@@ -1767,13 +1895,29 @@
       <c r="B48">
         <v>4.2139559999999996</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="4">
         <v>14.723947000000001</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="4"/>
-      <c r="I48" s="5"/>
+      <c r="D48">
+        <v>0.490562</v>
+      </c>
+      <c r="E48">
+        <v>9.7265960000000007</v>
+      </c>
+      <c r="F48" s="10">
+        <f t="shared" si="2"/>
+        <v>1.5137821083552765</v>
+      </c>
+      <c r="G48">
+        <v>0.450017</v>
+      </c>
+      <c r="H48">
+        <v>8.8808670000000003</v>
+      </c>
+      <c r="I48" s="10">
+        <f t="shared" si="3"/>
+        <v>1.6579402664176821</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
@@ -1782,13 +1926,29 @@
       <c r="B49">
         <v>4.5418440000000002</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="4">
         <v>14.086270000000001</v>
       </c>
-      <c r="D49" s="4"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="4"/>
-      <c r="I49" s="5"/>
+      <c r="D49">
+        <v>0.53921300000000005</v>
+      </c>
+      <c r="E49">
+        <v>9.9430709999999998</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4166920863785446</v>
+      </c>
+      <c r="G49">
+        <v>0.50582800000000006</v>
+      </c>
+      <c r="H49">
+        <v>9.3377540000000003</v>
+      </c>
+      <c r="I49" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5085287104372207</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
@@ -1797,13 +1957,29 @@
       <c r="B50">
         <v>4.7881710000000002</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="4">
         <v>14.306535</v>
       </c>
-      <c r="D50" s="4"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="4"/>
-      <c r="I50" s="5"/>
+      <c r="D50">
+        <v>0.59807999999999995</v>
+      </c>
+      <c r="E50">
+        <v>11.698138999999999</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="2"/>
+        <v>1.2229752954722115</v>
+      </c>
+      <c r="G50">
+        <v>0.50907999999999998</v>
+      </c>
+      <c r="H50">
+        <v>11.227321999999999</v>
+      </c>
+      <c r="I50" s="10">
+        <f t="shared" si="3"/>
+        <v>1.2742606830016989</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
@@ -1812,13 +1988,29 @@
       <c r="B51">
         <v>5.1194030000000001</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="4">
         <v>16.77722</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="4"/>
-      <c r="I51" s="5"/>
+      <c r="D51">
+        <v>0.59258699999999997</v>
+      </c>
+      <c r="E51">
+        <v>11.717784</v>
+      </c>
+      <c r="F51" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4317741306718061</v>
+      </c>
+      <c r="G51">
+        <v>0.53839099999999995</v>
+      </c>
+      <c r="H51">
+        <v>11.739910999999999</v>
+      </c>
+      <c r="I51" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4290755696529558</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
@@ -1827,13 +2019,29 @@
       <c r="B52">
         <v>5.5305020000000003</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="4">
         <v>18.731389</v>
       </c>
-      <c r="D52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="4"/>
-      <c r="I52" s="5"/>
+      <c r="D52">
+        <v>0.67846399999999996</v>
+      </c>
+      <c r="E52">
+        <v>12.544979</v>
+      </c>
+      <c r="F52" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4931383304826578</v>
+      </c>
+      <c r="G52">
+        <v>0.56035100000000004</v>
+      </c>
+      <c r="H52">
+        <v>11.808135999999999</v>
+      </c>
+      <c r="I52" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5863120987088903</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
@@ -1842,13 +2050,29 @@
       <c r="B53">
         <v>5.9119820000000001</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="4">
         <v>19.619128</v>
       </c>
-      <c r="D53" s="4"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="4"/>
-      <c r="I53" s="5"/>
+      <c r="D53">
+        <v>0.672929</v>
+      </c>
+      <c r="E53">
+        <v>13.983955</v>
+      </c>
+      <c r="F53" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4029741943534573</v>
+      </c>
+      <c r="G53">
+        <v>0.58755999999999997</v>
+      </c>
+      <c r="H53">
+        <v>12.671239</v>
+      </c>
+      <c r="I53" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5483196236768955</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
@@ -1857,13 +2081,29 @@
       <c r="B54">
         <v>6.2716409999999998</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="4">
         <v>19.129785999999999</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="4"/>
-      <c r="I54" s="5"/>
+      <c r="D54">
+        <v>0.63609400000000005</v>
+      </c>
+      <c r="E54">
+        <v>13.642073999999999</v>
+      </c>
+      <c r="F54" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4022637613606259</v>
+      </c>
+      <c r="G54">
+        <v>0.60127600000000003</v>
+      </c>
+      <c r="H54">
+        <v>13.742995000000001</v>
+      </c>
+      <c r="I54" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3919663071986854</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
@@ -1872,13 +2112,29 @@
       <c r="B55">
         <v>6.5090339999999998</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="4">
         <v>19.475451</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="4"/>
-      <c r="I55" s="5"/>
+      <c r="D55">
+        <v>0.71536999999999995</v>
+      </c>
+      <c r="E55">
+        <v>14.196707999999999</v>
+      </c>
+      <c r="F55" s="10">
+        <f t="shared" si="2"/>
+        <v>1.3718286661950081</v>
+      </c>
+      <c r="G55">
+        <v>0.60342200000000001</v>
+      </c>
+      <c r="H55">
+        <v>15.776018000000001</v>
+      </c>
+      <c r="I55" s="10">
+        <f t="shared" si="3"/>
+        <v>1.234497260335276</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
@@ -1887,13 +2143,29 @@
       <c r="B56">
         <v>6.8923880000000004</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="4">
         <v>20.863251999999999</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="4"/>
-      <c r="I56" s="5"/>
+      <c r="D56">
+        <v>0.73385199999999995</v>
+      </c>
+      <c r="E56">
+        <v>13.805649000000001</v>
+      </c>
+      <c r="F56" s="10">
+        <f t="shared" si="2"/>
+        <v>1.5112112440349597</v>
+      </c>
+      <c r="G56">
+        <v>0.61862700000000004</v>
+      </c>
+      <c r="H56">
+        <v>15.181255999999999</v>
+      </c>
+      <c r="I56" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3742770690382931</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
@@ -1902,13 +2174,29 @@
       <c r="B57">
         <v>7.5221939999999998</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="4">
         <v>31.162883999999998</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="4"/>
-      <c r="I57" s="5"/>
+      <c r="D57">
+        <v>0.72900399999999999</v>
+      </c>
+      <c r="E57">
+        <v>14.737897</v>
+      </c>
+      <c r="F57" s="10">
+        <f t="shared" si="2"/>
+        <v>2.1144729129264506</v>
+      </c>
+      <c r="G57">
+        <v>0.660883</v>
+      </c>
+      <c r="H57">
+        <v>15.418733</v>
+      </c>
+      <c r="I57" s="10">
+        <f t="shared" si="3"/>
+        <v>2.02110536579108</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
@@ -1917,13 +2205,29 @@
       <c r="B58">
         <v>7.5826880000000001</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="4">
         <v>24.242832</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="4"/>
-      <c r="I58" s="5"/>
+      <c r="D58">
+        <v>0.81065500000000001</v>
+      </c>
+      <c r="E58">
+        <v>15.248659999999999</v>
+      </c>
+      <c r="F58" s="10">
+        <f t="shared" si="2"/>
+        <v>1.5898335984932448</v>
+      </c>
+      <c r="G58">
+        <v>0.70172100000000004</v>
+      </c>
+      <c r="H58">
+        <v>15.947858999999999</v>
+      </c>
+      <c r="I58" s="10">
+        <f t="shared" si="3"/>
+        <v>1.52013082132216</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
@@ -1932,13 +2236,29 @@
       <c r="B59">
         <v>7.928973</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="4">
         <v>23.477260000000001</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="4"/>
-      <c r="I59" s="5"/>
+      <c r="D59">
+        <v>0.80369699999999999</v>
+      </c>
+      <c r="E59">
+        <v>18.574337</v>
+      </c>
+      <c r="F59" s="10">
+        <f t="shared" si="2"/>
+        <v>1.263962207641651</v>
+      </c>
+      <c r="G59">
+        <v>0.75986100000000001</v>
+      </c>
+      <c r="H59">
+        <v>20.227391999999998</v>
+      </c>
+      <c r="I59" s="10">
+        <f t="shared" si="3"/>
+        <v>1.1606666840688113</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
@@ -1947,13 +2267,29 @@
       <c r="B60">
         <v>8.360716</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="4">
         <v>26.170957999999999</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="4"/>
-      <c r="I60" s="5"/>
+      <c r="D60">
+        <v>0.865622</v>
+      </c>
+      <c r="E60">
+        <v>18.512557999999999</v>
+      </c>
+      <c r="F60" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4136867525276626</v>
+      </c>
+      <c r="G60">
+        <v>0.74780400000000002</v>
+      </c>
+      <c r="H60">
+        <v>17.660693999999999</v>
+      </c>
+      <c r="I60" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4818759670486334</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
@@ -1962,13 +2298,29 @@
       <c r="B61">
         <v>8.7009120000000006</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="4">
         <v>24.775784999999999</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="4"/>
-      <c r="I61" s="5"/>
+      <c r="D61">
+        <v>0.90172200000000002</v>
+      </c>
+      <c r="E61">
+        <v>18.018979000000002</v>
+      </c>
+      <c r="F61" s="10">
+        <f t="shared" si="2"/>
+        <v>1.3749827334834008</v>
+      </c>
+      <c r="G61">
+        <v>0.76293500000000003</v>
+      </c>
+      <c r="H61">
+        <v>17.953451000000001</v>
+      </c>
+      <c r="I61" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3800012599249023</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
@@ -1977,13 +2329,29 @@
       <c r="B62">
         <v>9.1592319999999994</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="4">
         <v>26.441016000000001</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="4"/>
-      <c r="I62" s="5"/>
+      <c r="D62">
+        <v>0.94251499999999999</v>
+      </c>
+      <c r="E62">
+        <v>18.242404000000001</v>
+      </c>
+      <c r="F62" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4494260734495301</v>
+      </c>
+      <c r="G62">
+        <v>0.78579200000000005</v>
+      </c>
+      <c r="H62">
+        <v>18.318173999999999</v>
+      </c>
+      <c r="I62" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4434307699009739</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
@@ -1992,13 +2360,29 @@
       <c r="B63">
         <v>9.6805749999999993</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="4">
         <v>28.407530000000001</v>
       </c>
-      <c r="D63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="4"/>
-      <c r="I63" s="5"/>
+      <c r="D63">
+        <v>0.97005200000000003</v>
+      </c>
+      <c r="E63">
+        <v>20.141197999999999</v>
+      </c>
+      <c r="F63" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4104190823207241</v>
+      </c>
+      <c r="G63">
+        <v>0.77426200000000001</v>
+      </c>
+      <c r="H63">
+        <v>20.153303000000001</v>
+      </c>
+      <c r="I63" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4095719197989531</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
@@ -2007,13 +2391,29 @@
       <c r="B64">
         <v>9.9461390000000005</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="4">
         <v>26.448874</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="4"/>
-      <c r="I64" s="5"/>
+      <c r="D64">
+        <v>0.99459699999999995</v>
+      </c>
+      <c r="E64">
+        <v>15.539987</v>
+      </c>
+      <c r="F64" s="10">
+        <f t="shared" si="2"/>
+        <v>1.7019881676863693</v>
+      </c>
+      <c r="G64">
+        <v>0.80645500000000003</v>
+      </c>
+      <c r="H64">
+        <v>19.886838999999998</v>
+      </c>
+      <c r="I64" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3299687295703455</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
@@ -2022,13 +2422,29 @@
       <c r="B65">
         <v>10.683282999999999</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="4">
         <v>29.509153999999999</v>
       </c>
-      <c r="D65" s="4"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="4"/>
-      <c r="I65" s="5"/>
+      <c r="D65">
+        <v>1.030402</v>
+      </c>
+      <c r="E65">
+        <v>17.810224999999999</v>
+      </c>
+      <c r="F65" s="10">
+        <f t="shared" si="2"/>
+        <v>1.65686587339576</v>
+      </c>
+      <c r="G65">
+        <v>0.84604000000000001</v>
+      </c>
+      <c r="H65">
+        <v>21.025320000000001</v>
+      </c>
+      <c r="I65" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4035055827925567</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
@@ -2037,13 +2453,29 @@
       <c r="B66">
         <v>10.981681</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="4">
         <v>28.635020000000001</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="4"/>
-      <c r="I66" s="5"/>
+      <c r="D66">
+        <v>1.056154</v>
+      </c>
+      <c r="E66">
+        <v>22.130542999999999</v>
+      </c>
+      <c r="F66" s="10">
+        <f t="shared" si="2"/>
+        <v>1.2939140264204092</v>
+      </c>
+      <c r="G66">
+        <v>0.889208</v>
+      </c>
+      <c r="H66">
+        <v>21.917853999999998</v>
+      </c>
+      <c r="I66" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3064700586106652</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
@@ -2052,13 +2484,29 @@
       <c r="B67">
         <v>11.572463000000001</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="4">
         <v>32.200043999999998</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="4"/>
-      <c r="I67" s="5"/>
+      <c r="D67">
+        <v>1.186229</v>
+      </c>
+      <c r="E67">
+        <v>24.612438999999998</v>
+      </c>
+      <c r="F67" s="10">
+        <f t="shared" si="2"/>
+        <v>1.3082833440440422</v>
+      </c>
+      <c r="G67">
+        <v>0.91731099999999999</v>
+      </c>
+      <c r="H67">
+        <v>22.054908000000001</v>
+      </c>
+      <c r="I67" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4599944828606854</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
@@ -2067,13 +2515,29 @@
       <c r="B68">
         <v>11.990257</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="4">
         <v>33.297845000000002</v>
       </c>
-      <c r="D68" s="4"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="4"/>
-      <c r="I68" s="5"/>
+      <c r="D68">
+        <v>1.1530389999999999</v>
+      </c>
+      <c r="E68">
+        <v>22.171119000000001</v>
+      </c>
+      <c r="F68" s="10">
+        <f t="shared" si="2"/>
+        <v>1.5018567623943564</v>
+      </c>
+      <c r="G68">
+        <v>0.93183000000000005</v>
+      </c>
+      <c r="H68">
+        <v>20.696251</v>
+      </c>
+      <c r="I68" s="10">
+        <f t="shared" si="3"/>
+        <v>1.6088829324692671</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
@@ -2082,31 +2546,63 @@
       <c r="B69">
         <v>12.124834999999999</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="4">
         <v>32.234180000000002</v>
       </c>
-      <c r="D69" s="4"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="4"/>
-      <c r="I69" s="5"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D69">
+        <v>1.182485</v>
+      </c>
+      <c r="E69">
+        <v>21.834859000000002</v>
+      </c>
+      <c r="F69" s="10">
+        <f t="shared" si="2"/>
+        <v>1.4762714977916733</v>
+      </c>
+      <c r="G69">
+        <v>0.99179099999999998</v>
+      </c>
+      <c r="H69">
+        <v>22.357597999999999</v>
+      </c>
+      <c r="I69" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4417550579449547</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>40000000</v>
       </c>
       <c r="B70">
         <v>12.632493</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="11">
         <v>39.300693000000003</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="4"/>
-      <c r="I70" s="5"/>
+      <c r="D70">
+        <v>1.2178329999999999</v>
+      </c>
+      <c r="E70">
+        <v>19.064277000000001</v>
+      </c>
+      <c r="F70" s="10">
+        <f t="shared" si="2"/>
+        <v>2.0614835275421144</v>
+      </c>
+      <c r="G70">
+        <v>1.023355</v>
+      </c>
+      <c r="H70">
+        <v>21.716097000000001</v>
+      </c>
+      <c r="I70" s="10">
+        <f t="shared" si="3"/>
+        <v>1.8097493762345969</v>
+      </c>
     </row>
     <row r="75" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Lab 02/RunningTimeRecording.xlsx
+++ b/Lab 02/RunningTimeRecording.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\Lab 02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F4A27-63DE-4E60-95B6-FD63419CBE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runtime" sheetId="1" r:id="rId1"/>
@@ -246,6 +246,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -254,12 +260,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,43 +542,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="12" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="12" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="12" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="13"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>10000000</v>
       </c>
@@ -644,7 +644,7 @@
         <v>1.3503039831807164</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>11000000</v>
       </c>
@@ -675,7 +675,7 @@
         <v>1.4314321789308464</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>12000000</v>
       </c>
@@ -706,7 +706,7 @@
         <v>1.3990388485014549</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>13000000</v>
       </c>
@@ -737,7 +737,7 @@
         <v>1.4162593677956241</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>14000000</v>
       </c>
@@ -768,7 +768,7 @@
         <v>1.4353413689728149</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>15000000</v>
       </c>
@@ -799,7 +799,7 @@
         <v>1.4958510931601727</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>16000000</v>
       </c>
@@ -830,7 +830,7 @@
         <v>1.4946658808534796</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>17000000</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1.5314277225416137</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>18000000</v>
       </c>
@@ -892,7 +892,7 @@
         <v>1.7010684087007899</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>19000000</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1.8466274211032072</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>20000000</v>
       </c>
@@ -954,7 +954,7 @@
         <v>1.9658831253344848</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>21000000</v>
       </c>
@@ -985,7 +985,7 @@
         <v>1.6905367661533188</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>22000000</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>1.4562076078036108</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>23000000</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>1.4736406545695642</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>24000000</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>1.5024524352787376</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>25000000</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>1.3807101680016927</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>26000000</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>1.4815484367362499</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>27000000</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>1.4320888444651907</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>28000000</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>1.4896735870398701</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>29000000</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>1.4574478596011657</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>30000000</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>1.471640083333507</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>31000000</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>1.4480301190510056</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>32000000</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>1.4799671594867332</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>33000000</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>1.4870401475364317</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>34000000</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>1.4523169715947184</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>35000000</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>1.4342921380463396</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>36000000</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>1.6968519767772656</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>37000000</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>1.5276332531432211</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>38000000</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>1.6903936314613837</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>39000000</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>1.4135842256219358</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>40000000</v>
       </c>
@@ -1574,38 +1574,38 @@
         <v>1.4963832739552605</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="15"/>
+      <c r="D38" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="12" t="s">
+      <c r="E38" s="16"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="14" t="s">
+      <c r="H38" s="16"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="13"/>
       <c r="B39" s="5" t="s">
         <v>7</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>10000000</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>1.2404784823894681</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>11000000</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>1.2744177730313988</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>12000000</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>1.5768721682293738</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>13000000</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>1.4027845914718184</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>14000000</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>1.4486742368784218</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>15000000</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1.3330253848550908</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>16000000</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>1.5375576433617986</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>17000000</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>1.4187548742936833</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>18000000</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>1.6579402664176821</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>19000000</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>1.5085287104372207</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>20000000</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>1.2742606830016989</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>21000000</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>1.4290755696529558</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>22000000</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>1.5863120987088903</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>23000000</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>1.5483196236768955</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>24000000</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>1.3919663071986854</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>25000000</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>1.234497260335276</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>26000000</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>1.3742770690382931</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>27000000</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>2.02110536579108</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>28000000</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>1.52013082132216</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>29000000</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>1.1606666840688113</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>30000000</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>1.4818759670486334</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>31000000</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>1.3800012599249023</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>32000000</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>1.4434307699009739</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>33000000</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>1.4095719197989531</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>34000000</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>1.3299687295703455</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>35000000</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>1.4035055827925567</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>36000000</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>1.3064700586106652</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>37000000</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>1.4599944828606854</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>38000000</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>1.6088829324692671</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>39000000</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>1.4417550579449547</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3">
         <v>40000000</v>
       </c>
@@ -2601,23 +2601,23 @@
         <v>1.8097493762345969</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="J38:L38"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
